--- a/Echohaven_Airbnb_Tracker_Updated.xlsx
+++ b/Echohaven_Airbnb_Tracker_Updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim_abiok/Desktop/PROJECTS/TIMOTHY ABIOK/ECHOHAVEN /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192015D5-0A82-B944-8B0A-2A7CE7FCFF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65822EBB-0EA6-CD49-9833-DCC2BC51B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="1760" windowWidth="24760" windowHeight="14600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Echohaven Tracker" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="50">
   <si>
     <t>ECHOHAVEN AIRBNB</t>
   </si>
@@ -137,6 +137,42 @@
   </si>
   <si>
     <t>LOW</t>
+  </si>
+  <si>
+    <t>Bottled Water</t>
+  </si>
+  <si>
+    <t>Towels</t>
+  </si>
+  <si>
+    <t>Soaps</t>
+  </si>
+  <si>
+    <t>Humidifier &amp; Oils</t>
+  </si>
+  <si>
+    <t>Electronic Locks</t>
+  </si>
+  <si>
+    <t>Doors</t>
+  </si>
+  <si>
+    <t>Bedroom Desk</t>
+  </si>
+  <si>
+    <t>Upgrade</t>
+  </si>
+  <si>
+    <t>Flower Pots</t>
+  </si>
+  <si>
+    <t>Front Door Canopy</t>
+  </si>
+  <si>
+    <t>Pool Cushions</t>
+  </si>
+  <si>
+    <t>Pool Furniture</t>
   </si>
 </sst>
 </file>
@@ -215,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,11 +268,37 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -593,8 +655,9 @@
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="8.5" customWidth="1"/>
+    <col min="6" max="6" width="15" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.25">
@@ -705,7 +768,7 @@
         <v>33</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -729,7 +792,7 @@
         <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -803,7 +866,7 @@
         <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -851,7 +914,7 @@
         <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -877,7 +940,7 @@
         <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1033,114 +1096,254 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>9</v>
+      </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="E19" s="4">
+        <v>300</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="E20" s="4">
+        <v>500</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="E21" s="4">
+        <v>500</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="E22" s="4">
+        <v>500</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="F23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="F24" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="F25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="F26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="4"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="F27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
+      <c r="F28" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="4"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
+      <c r="F29" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
@@ -1148,7 +1351,7 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="3"/>
+      <c r="F30" s="8"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
     </row>
@@ -1158,7 +1361,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="4"/>
-      <c r="F31" s="3"/>
+      <c r="F31" s="8"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
     </row>
@@ -1168,7 +1371,7 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="4"/>
-      <c r="F32" s="3"/>
+      <c r="F32" s="8"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
     </row>
@@ -1178,7 +1381,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="4"/>
-      <c r="F33" s="3"/>
+      <c r="F33" s="8"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
@@ -1188,7 +1391,7 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="4"/>
-      <c r="F34" s="3"/>
+      <c r="F34" s="8"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
     </row>
@@ -1198,7 +1401,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
-      <c r="F35" s="3"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
     </row>
@@ -1208,7 +1411,7 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="4"/>
-      <c r="F36" s="3"/>
+      <c r="F36" s="8"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
@@ -1218,7 +1421,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="3"/>
+      <c r="F37" s="8"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
     </row>
@@ -1228,7 +1431,7 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
-      <c r="F38" s="3"/>
+      <c r="F38" s="8"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
     </row>
@@ -1238,7 +1441,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="3"/>
+      <c r="F39" s="8"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
@@ -1248,7 +1451,7 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="4"/>
-      <c r="F40" s="3"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
     </row>
@@ -1258,7 +1461,7 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="4"/>
-      <c r="F41" s="3"/>
+      <c r="F41" s="8"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
     </row>
@@ -1268,7 +1471,7 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="4"/>
-      <c r="F42" s="3"/>
+      <c r="F42" s="8"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
@@ -1278,7 +1481,7 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="4"/>
-      <c r="F43" s="3"/>
+      <c r="F43" s="8"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
     </row>
@@ -1288,7 +1491,7 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="3"/>
+      <c r="F44" s="8"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
     </row>
@@ -1298,7 +1501,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="4"/>
-      <c r="F45" s="3"/>
+      <c r="F45" s="8"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
@@ -1308,7 +1511,7 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="4"/>
-      <c r="F46" s="3"/>
+      <c r="F46" s="8"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
     </row>
@@ -1318,7 +1521,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="3"/>
+      <c r="F47" s="8"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
     </row>
@@ -1328,7 +1531,7 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="3"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
@@ -1338,7 +1541,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="3"/>
+      <c r="F49" s="8"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
     </row>
@@ -1348,7 +1551,7 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="3"/>
+      <c r="F50" s="8"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
@@ -1358,7 +1561,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="3"/>
+      <c r="F51" s="8"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
@@ -1368,7 +1571,7 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="3"/>
+      <c r="F52" s="8"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
     </row>
@@ -1378,7 +1581,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="4"/>
-      <c r="F53" s="3"/>
+      <c r="F53" s="8"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
     </row>
@@ -1388,7 +1591,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
-      <c r="F54" s="3"/>
+      <c r="F54" s="8"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
@@ -1398,7 +1601,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
-      <c r="F55" s="3"/>
+      <c r="F55" s="8"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
     </row>
@@ -1408,7 +1611,7 @@
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
-      <c r="F56" s="3"/>
+      <c r="F56" s="8"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
     </row>
@@ -1418,7 +1621,7 @@
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="4"/>
-      <c r="F57" s="3"/>
+      <c r="F57" s="8"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
@@ -1428,7 +1631,7 @@
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="4"/>
-      <c r="F58" s="3"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
@@ -1438,7 +1641,7 @@
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="4"/>
-      <c r="F59" s="3"/>
+      <c r="F59" s="8"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
     </row>
@@ -1448,7 +1651,7 @@
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="4"/>
-      <c r="F60" s="3"/>
+      <c r="F60" s="8"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
     </row>
@@ -1458,7 +1661,7 @@
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="4"/>
-      <c r="F61" s="3"/>
+      <c r="F61" s="8"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
@@ -1468,7 +1671,7 @@
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="4"/>
-      <c r="F62" s="3"/>
+      <c r="F62" s="8"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
@@ -1478,7 +1681,7 @@
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="4"/>
-      <c r="F63" s="3"/>
+      <c r="F63" s="8"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
     </row>
@@ -1488,7 +1691,7 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="4"/>
-      <c r="F64" s="3"/>
+      <c r="F64" s="8"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
     </row>
@@ -1498,7 +1701,7 @@
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="4"/>
-      <c r="F65" s="3"/>
+      <c r="F65" s="8"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
     </row>
@@ -1508,7 +1711,7 @@
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="4"/>
-      <c r="F66" s="3"/>
+      <c r="F66" s="8"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
@@ -1518,7 +1721,7 @@
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="4"/>
-      <c r="F67" s="3"/>
+      <c r="F67" s="8"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
     </row>
@@ -1528,7 +1731,7 @@
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="4"/>
-      <c r="F68" s="3"/>
+      <c r="F68" s="8"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
     </row>
@@ -1538,7 +1741,7 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="4"/>
-      <c r="F69" s="3"/>
+      <c r="F69" s="8"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
     </row>
@@ -1548,7 +1751,7 @@
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="3"/>
+      <c r="F70" s="8"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
@@ -1558,7 +1761,7 @@
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
-      <c r="F71" s="3"/>
+      <c r="F71" s="8"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
@@ -1568,7 +1771,7 @@
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="4"/>
-      <c r="F72" s="3"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
@@ -1578,7 +1781,7 @@
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="4"/>
-      <c r="F73" s="3"/>
+      <c r="F73" s="8"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
@@ -1588,7 +1791,7 @@
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="4"/>
-      <c r="F74" s="3"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
     </row>
@@ -1598,7 +1801,7 @@
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="4"/>
-      <c r="F75" s="3"/>
+      <c r="F75" s="8"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
@@ -1608,7 +1811,7 @@
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="4"/>
-      <c r="F76" s="3"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
     </row>
@@ -1618,7 +1821,7 @@
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="4"/>
-      <c r="F77" s="3"/>
+      <c r="F77" s="8"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
@@ -1628,7 +1831,7 @@
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="4"/>
-      <c r="F78" s="3"/>
+      <c r="F78" s="8"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
     </row>
@@ -1638,7 +1841,7 @@
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="4"/>
-      <c r="F79" s="3"/>
+      <c r="F79" s="8"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
@@ -1648,7 +1851,7 @@
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="4"/>
-      <c r="F80" s="3"/>
+      <c r="F80" s="8"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
     </row>
@@ -1658,7 +1861,7 @@
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="4"/>
-      <c r="F81" s="3"/>
+      <c r="F81" s="8"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
     </row>
@@ -1668,7 +1871,7 @@
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="4"/>
-      <c r="F82" s="3"/>
+      <c r="F82" s="8"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
     </row>
@@ -1678,7 +1881,7 @@
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="4"/>
-      <c r="F83" s="3"/>
+      <c r="F83" s="8"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
     </row>
@@ -1688,7 +1891,7 @@
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="4"/>
-      <c r="F84" s="3"/>
+      <c r="F84" s="8"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
     </row>
@@ -1698,7 +1901,7 @@
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="4"/>
-      <c r="F85" s="3"/>
+      <c r="F85" s="8"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
     </row>
@@ -1708,7 +1911,7 @@
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="4"/>
-      <c r="F86" s="3"/>
+      <c r="F86" s="8"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
     </row>
@@ -1718,7 +1921,7 @@
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="4"/>
-      <c r="F87" s="3"/>
+      <c r="F87" s="8"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
     </row>
@@ -1728,7 +1931,7 @@
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="4"/>
-      <c r="F88" s="3"/>
+      <c r="F88" s="8"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
     </row>
@@ -1738,7 +1941,7 @@
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="4"/>
-      <c r="F89" s="3"/>
+      <c r="F89" s="8"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
     </row>
@@ -1748,7 +1951,7 @@
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="4"/>
-      <c r="F90" s="3"/>
+      <c r="F90" s="8"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
     </row>
@@ -1758,7 +1961,7 @@
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="4"/>
-      <c r="F91" s="3"/>
+      <c r="F91" s="8"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
     </row>
@@ -1768,7 +1971,7 @@
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="4"/>
-      <c r="F92" s="3"/>
+      <c r="F92" s="8"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
     </row>
@@ -1778,7 +1981,7 @@
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="4"/>
-      <c r="F93" s="3"/>
+      <c r="F93" s="8"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
     </row>
@@ -1788,7 +1991,7 @@
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="4"/>
-      <c r="F94" s="3"/>
+      <c r="F94" s="8"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
     </row>
@@ -1798,7 +2001,7 @@
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="4"/>
-      <c r="F95" s="3"/>
+      <c r="F95" s="8"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
     </row>
@@ -1808,7 +2011,7 @@
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
-      <c r="F96" s="3"/>
+      <c r="F96" s="8"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
     </row>
@@ -1818,7 +2021,7 @@
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="4"/>
-      <c r="F97" s="3"/>
+      <c r="F97" s="8"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
     </row>
@@ -1828,7 +2031,7 @@
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="4"/>
-      <c r="F98" s="3"/>
+      <c r="F98" s="8"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
     </row>
@@ -1838,7 +2041,7 @@
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="4"/>
-      <c r="F99" s="3"/>
+      <c r="F99" s="8"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
     </row>
@@ -1848,7 +2051,7 @@
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
-      <c r="F100" s="3"/>
+      <c r="F100" s="8"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
     </row>
@@ -1858,20 +2061,20 @@
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <conditionalFormatting sqref="J6">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="HIGH">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",J6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H18">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="HIGH">
+  <conditionalFormatting sqref="A3:H18 C19:C22 E19:E22 A19:A29 G19:H29">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="MEDIUM">
+      <formula>NOT(ISERROR(SEARCH("MEDIUM",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="HIGH">
       <formula>NOT(ISERROR(SEARCH("HIGH",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="MEDIUM">
-      <formula>NOT(ISERROR(SEARCH("MEDIUM",A3)))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H18">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="LOW">
+  <conditionalFormatting sqref="H3:H29">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",H3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1882,7 +2085,7 @@
     <dataValidation type="list" allowBlank="1" sqref="F3:F100" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Daily,Weekly,Monthly,Quarterly,Annual,One-time"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H18" xr:uid="{CF17E1F0-C91A-0A49-9E62-70273AEE4C5C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H29" xr:uid="{CF17E1F0-C91A-0A49-9E62-70273AEE4C5C}">
       <formula1>"HIGH,LOW,MEDIUM"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Echohaven_Airbnb_Tracker_Updated.xlsx
+++ b/Echohaven_Airbnb_Tracker_Updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tim_abiok/Desktop/PROJECTS/TIMOTHY ABIOK/ECHOHAVEN /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65822EBB-0EA6-CD49-9833-DCC2BC51B42C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F830F645-8583-F24E-BCE4-BC68021B3564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3000" yWindow="1760" windowWidth="24760" windowHeight="14600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,27 @@
     <sheet name="Echohaven Tracker" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Echohaven Tracker'!$A$2:$H$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Echohaven Tracker'!$A$2:$H$29</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="51">
   <si>
     <t>ECHOHAVEN AIRBNB</t>
   </si>
@@ -173,6 +186,9 @@
   </si>
   <si>
     <t>Pool Furniture</t>
+  </si>
+  <si>
+    <t>Smoke Detector</t>
   </si>
 </sst>
 </file>
@@ -278,7 +294,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -326,16 +342,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -744,7 +750,7 @@
         <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -937,7 +943,7 @@
         <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>36</v>
@@ -1346,14 +1352,26 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
+      <c r="F30" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
@@ -2056,7 +2074,7 @@
       <c r="H100" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:H18" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:H29" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -2065,7 +2083,7 @@
       <formula>NOT(ISERROR(SEARCH("HIGH",J6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:H18 C19:C22 E19:E22 A19:A29 G19:H29">
+  <conditionalFormatting sqref="A3:H18 C19:C22 E19:E22 A19:A30 G19:H30">
     <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="MEDIUM">
       <formula>NOT(ISERROR(SEARCH("MEDIUM",A3)))</formula>
     </cfRule>
@@ -2073,7 +2091,7 @@
       <formula>NOT(ISERROR(SEARCH("HIGH",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H29">
+  <conditionalFormatting sqref="H3:H30">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="LOW">
       <formula>NOT(ISERROR(SEARCH("LOW",H3)))</formula>
     </cfRule>
@@ -2085,7 +2103,7 @@
     <dataValidation type="list" allowBlank="1" sqref="F3:F100" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Daily,Weekly,Monthly,Quarterly,Annual,One-time"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H29" xr:uid="{CF17E1F0-C91A-0A49-9E62-70273AEE4C5C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H30" xr:uid="{CF17E1F0-C91A-0A49-9E62-70273AEE4C5C}">
       <formula1>"HIGH,LOW,MEDIUM"</formula1>
     </dataValidation>
   </dataValidations>
